--- a/greece-itinerary.xlsx
+++ b/greece-itinerary.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -186,6 +186,20 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="32">
@@ -369,7 +383,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -572,6 +586,13 @@
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2866,49 +2887,49 @@
           <t>22.10.2026 – יום ה׳</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="98" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" s="99" t="inlineStr">
         <is>
           <t>פורטאריה</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>מקריניצה</t>
-        </is>
-      </c>
-      <c r="E61" s="17" t="inlineStr">
-        <is>
-          <t>Makrinitsa Central Square</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="D61" s="99" t="inlineStr">
+        <is>
+          <t>מקריניצה – המרפסת של פיליון ⭐ חובה</t>
+        </is>
+      </c>
+      <c r="E61" s="100" t="inlineStr">
+        <is>
+          <t>Makrinitsa Central Square – Balcony of Pelion</t>
+        </is>
+      </c>
+      <c r="F61" s="98" t="inlineStr">
         <is>
           <t>15–20 דק׳</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G61" s="98" t="inlineStr">
         <is>
           <t>1:15–1:30 ש׳</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H61" s="98" t="inlineStr">
         <is>
           <t>חניה בכניסה</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>“המרפסת של פיליון” – סמטאות ללא רכב, כיכר ותצפית נהדרת על וולוס והמפרץ.</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>הליכה בעלייה ובאבנים; נעליים נוחות.</t>
+      <c r="I61" s="99" t="inlineStr">
+        <is>
+          <t>אחת מנקודות החובה של פיליון. מהכיכר המרכזית של מקריניצה נפתחת תצפית פנורמית מרהיבה על וולוס ועל המפרץ הפגסטי, וזו הסיבה שהכפר מכונה “המרפסת של פיליון”. מטיילים בסמטאות האבן ללא רכבים, רואים בתי אחוזה מסורתיים, מזרקות אבן ועץ דולב גדול, ויושבים לקפה מול הנוף.</t>
+        </is>
+      </c>
+      <c r="J61" s="99" t="inlineStr">
+        <is>
+          <t>חובה במסלול. חונים בכניסה לכפר וממשיכים ברגל לכיכר; נעליים נוחות בגלל אבני הרחוב והעליות.</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3865,7 @@
       </c>
       <c r="B93" s="68" t="inlineStr">
         <is>
-          <t>Pelion – Portaria, Makrinitsa, Tsagarada, Damouchari</t>
+          <t>Pelion – Portaria → Makrinitsa (המרפסת של פיליון ⭐ חובה) → Tsagarada → Damouchari</t>
         </is>
       </c>
       <c r="C93" s="17" t="inlineStr">
@@ -3854,7 +3875,7 @@
       </c>
       <c r="D93" s="68" t="inlineStr">
         <is>
-          <t>כפרי פיליון וחוף</t>
+          <t>כפרי פיליון, תצפית החובה ממקריניצה וחוף</t>
         </is>
       </c>
       <c r="E93" s="68" t="inlineStr">
